--- a/tools/importer/reports/import-tcs-homepage.report.xlsx
+++ b/tools/importer/reports/import-tcs-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>tcs-homepage</t>
   </si>
   <si>
-    <t>2026-03-11T12:56:58.682Z</t>
+    <t>2026-03-11T13:23:44.588Z</t>
   </si>
   <si>
     <t>Tata Consultancy Services: Building Perpetually Adaptive Enterprises</t>

--- a/tools/importer/reports/import-tcs-homepage.report.xlsx
+++ b/tools/importer/reports/import-tcs-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>tcs-homepage</t>
   </si>
   <si>
-    <t>2026-03-11T13:23:44.588Z</t>
+    <t>2026-03-12T11:34:02.707Z</t>
   </si>
   <si>
     <t>Tata Consultancy Services: Building Perpetually Adaptive Enterprises</t>

--- a/tools/importer/reports/import-tcs-homepage.report.xlsx
+++ b/tools/importer/reports/import-tcs-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>tcs-homepage</t>
   </si>
   <si>
-    <t>2026-03-12T11:34:02.707Z</t>
+    <t>2026-03-12T11:52:11.868Z</t>
   </si>
   <si>
     <t>Tata Consultancy Services: Building Perpetually Adaptive Enterprises</t>
